--- a/stories/arbres/ATOM-SAN.ALI.003-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Blanche joue au parc avec papa. Le soleil chauffe le toboggan. Blanche court. Sa bouche devient sèche. Elle a soif. Papa est près du banc. Blanche dit : j'ai soif, papa. Papa sourit. Ils rentrent à la maison. Dans la cuisine, papa prend un verre. Il verse de l'eau claire. Blanche prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore. Papa dit : quand on a soif, on boit de l'eau. Blanche pose le verre. Elle se sent mieux. Elle dit merci. Papa verse encore un peu. Blanche boit une dernière gorgée. L'eau coule douce dans sa gorge.</t>
+          <t>Blanche joue au parc avec papa. Le soleil chauffe le toboggan. Blanche court. Sa bouche devient sèche. Elle a soif. Papa est près du banc. J'ai soif, papa. Papa sourit. Ils rentrent à la maison. Dans la cuisine, papa prend un verre. Il verse de l'eau claire. Blanche prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore. Quand on a soif, on boit de l'eau. Blanche pose le verre. Elle se sent mieux. Elle dit merci. Papa verse encore un peu. Blanche boit une dernière gorgée. L'eau coule douce dans sa gorge.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Blanche joue au parc avec papa. Le soleil chauffe le toboggan. Blanche court. Sa bouche devient sèche. Elle a soif. Papa est près du banc.
+enfant-f|J'ai soif, papa. Papa sourit. Ils rentrent à la maison.
+narrateur|Dans la cuisine, papa prend un verre. Il verse de l'eau claire. Blanche prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore.
+papa|Quand on a soif, on boit de l'eau.
+narrateur|Blanche pose le verre. Elle se sent mieux. Elle dit merci. Papa verse encore un peu. Blanche boit une dernière gorgée. L'eau coule douce dans sa gorge.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Blanche a soif. Que prend-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Blanche avait soif. Elle a pris le verre. Elle a bu de l'eau. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Blanche retourne au jardin. Le verre reste sur la table.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Blanche pose le verre. Elle se sent mieux. Elle dit merci. Papa verse encore un peu. Blanche boit une dernière gorgée. L'eau coule douce dans sa gorge.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Blanche a soif. Que prend-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1683,7 @@
           <t>narrateur|Blanche avait soif. Elle a pris le verre. Elle a bu de l'eau. Papa était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1851,7 @@
           <t>narrateur|Blanche retourne au jardin. Le verre reste sur la table.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2062,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.003-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Blanche a soif au parc</t>
+          <t>Le toboggan chaud</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le toboggan est chaud comme un pain. Une cigale chante. Victorina a soif. Ils rentrent. Elle boit de l'eau dans un verre.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Blanche joue au parc avec papa. Le soleil chauffe le toboggan. Blanche court. Sa bouche devient sèche. Elle a soif. Papa est près du banc. J'ai soif, papa. Papa sourit. Ils rentrent à la maison. Dans la cuisine, papa prend un verre. Il verse de l'eau claire. Blanche prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore. Quand on a soif, on boit de l'eau. Blanche pose le verre. Elle se sent mieux. Elle dit merci. Papa verse encore un peu. Blanche boit une dernière gorgée. L'eau coule douce dans sa gorge.</t>
+          <t>Le toboggan est chaud comme un pain. Le métal brille, tout fort. Une cigale chante dans le platane. Les cheveux de Victorina collent un peu. Le parc sent l'herbe sèche. Victorina habite tout près, avec papa. Maman prépare le goûter, à la maison. Un banc attend à l'ombre. Tu as entendu la cigale, Victorina ? Elle chante, papa. Oui. Elle chante dans le platane. On s'assoit un moment sur le banc ? Oui, papa. Ils s'assoient à l'ombre. Le bois du banc est tiède. En ce moment, Victorina a soif. Sa bouche devient sèche. J'ai soif, papa. On rentre à la maison ? Oui. Ils rentrent. Leurs chaussures font clap, clap. Dans la cuisine, c'est plus frais. Viens. On prend un verre. Papa prend un verre. Il verse de l'eau claire. L'eau chante dans le verre. Tu prends le verre d'eau ? Victorina prend le verre. Elle boit une gorgée. C'est frais. Elle boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Victorina pose le verre. Tu te sens mieux ? Oui, papa. Bravo, Victorina. Tu as bu de l'eau. L'eau coule douce dans sa gorge. Tu restes près de la table ? Oui, papa. On est bien, ici. La cuisine est plus fraîche que le parc. Tu as encore la cigale dans l'oreille ? Un peu. Elle chante loin, maintenant. Victorina tient le verre à deux mains. Une goutte reste sur le bord.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1329,62 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Blanche joue au parc avec papa. Le soleil chauffe le toboggan. Blanche court. Sa bouche devient sèche. Elle a soif. Papa est près du banc.
-enfant-f|J'ai soif, papa. Papa sourit. Ils rentrent à la maison.
-narrateur|Dans la cuisine, papa prend un verre. Il verse de l'eau claire. Blanche prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore.
+          <t>narrateur|Le toboggan est chaud comme un pain.
+narrateur|Le métal brille, tout fort.
+narrateur|Une cigale chante dans le platane.
+narrateur|Les cheveux de Victorina collent un peu.
+narrateur|Le parc sent l'herbe sèche.
+narrateur|Victorina habite tout près, avec papa.
+narrateur|Maman prépare le goûter, à la maison.
+narrateur|Un banc attend à l'ombre.
+papa|Tu as entendu la cigale, Victorina ?
+enfant-f|Elle chante, papa.
+papa|Oui.
+papa|Elle chante dans le platane.
+papa|On s'assoit un moment sur le banc ?
+enfant-f|Oui, papa.
+narrateur|Ils s'assoient à l'ombre.
+narrateur|Le bois du banc est tiède.
+narrateur|En ce moment, Victorina a soif.
+narrateur|Sa bouche devient sèche.
+enfant-f|J'ai soif, papa.
+papa|On rentre à la maison ?
+enfant-f|Oui.
+narrateur|Ils rentrent.
+narrateur|Leurs chaussures font clap, clap.
+narrateur|Dans la cuisine, c'est plus frais.
+papa|Viens.
+papa|On prend un verre.
+narrateur|Papa prend un verre.
+narrateur|Il verse de l'eau claire.
+narrateur|L'eau chante dans le verre.
+papa|Tu prends le verre d'eau ?
+narrateur|Victorina prend le verre.
+narrateur|Elle boit une gorgée.
+narrateur|C'est frais.
+narrateur|Elle boit encore.
 papa|Quand on a soif, on boit de l'eau.
-narrateur|Blanche pose le verre. Elle se sent mieux. Elle dit merci. Papa verse encore un peu. Blanche boit une dernière gorgée. L'eau coule douce dans sa gorge.</t>
+papa|Dans un verre.
+narrateur|Victorina pose le verre.
+papa|Tu te sens mieux ?
+enfant-f|Oui, papa.
+papa|Bravo, Victorina.
+papa|Tu as bu de l'eau.
+narrateur|L'eau coule douce dans sa gorge.
+papa|Tu restes près de la table ?
+enfant-f|Oui, papa.
+papa|On est bien, ici.
+narrateur|La cuisine est plus fraîche que le parc.
+papa|Tu as encore la cigale dans l'oreille ?
+enfant-f|Un peu.
+papa|Elle chante loin, maintenant.
+narrateur|Victorina tient le verre à deux mains.
+narrateur|Une goutte reste sur le bord.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>enfants_parc,verre</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1411,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Blanche a soif. Que prend-elle ?</t>
+          <t>Victorina a soif. Que prend-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,7 +1571,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Blanche a soif. Que prend-elle ?</t>
+          <t>narrateur|Victorina a soif.
+narrateur|Que prend-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Blanche avait soif. Elle a pris le verre. Elle a bu de l'eau. Papa était là.</t>
+          <t>Victorina avait soif. Elle a pris le verre. Elle a bu de l'eau. Bravo. C'est du bon travail. C'est frais, papa. Oui. L'eau est fraîche. Tu veux encore une gorgée ? Oui. Papa verse encore un peu. Victorina boit une dernière gorgée. Elle pose le verre. Le verre reste sur la table ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,7 +1744,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Blanche avait soif. Elle a pris le verre. Elle a bu de l'eau. Papa était là.</t>
+          <t>narrateur|Victorina avait soif.
+narrateur|Elle a pris le verre.
+narrateur|Elle a bu de l'eau.
+papa|Bravo.
+papa|C'est du bon travail.
+enfant-f|C'est frais, papa.
+papa|Oui. L'eau est fraîche.
+papa|Tu veux encore une gorgée ?
+enfant-f|Oui.
+narrateur|Papa verse encore un peu.
+narrateur|Victorina boit une dernière gorgée.
+narrateur|Elle pose le verre.
+papa|Le verre reste sur la table ?
+enfant-f|Oui, papa.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1708,7 +1785,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Blanche retourne au jardin. Le verre reste sur la table.</t>
+          <t>On retourne au jardin ? Oui, papa. Victorina prend la main de papa. Le verre reste sur la table. Tu as fini de poser le verre ? Oui. Bravo. Dehors, le platane fait de l'ombre. La cigale chante encore, plus loin. Le toboggan est encore chaud, hein ? Oui. Comme un pain. On reste à l'ombre un moment ? Oui. Merci, papa. Merci, Victorina. Tu as bu de l'eau. Victorina reste près de papa. Le jardin est plus doux, maintenant. Tu as fini de te reposer ? Oui, papa. Bravo. Le banc à l'ombre attend encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1848,7 +1925,28 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Blanche retourne au jardin. Le verre reste sur la table.</t>
+          <t>papa|On retourne au jardin ?
+enfant-f|Oui, papa.
+narrateur|Victorina prend la main de papa.
+narrateur|Le verre reste sur la table.
+papa|Tu as fini de poser le verre ?
+enfant-f|Oui.
+papa|Bravo.
+narrateur|Dehors, le platane fait de l'ombre.
+narrateur|La cigale chante encore, plus loin.
+papa|Le toboggan est encore chaud, hein ?
+enfant-f|Oui. Comme un pain.
+papa|On reste à l'ombre un moment ?
+enfant-f|Oui.
+enfant-f|Merci, papa.
+papa|Merci, Victorina.
+papa|Tu as bu de l'eau.
+narrateur|Victorina reste près de papa.
+narrateur|Le jardin est plus doux, maintenant.
+papa|Tu as fini de te reposer ?
+enfant-f|Oui, papa.
+papa|Bravo.
+narrateur|Le banc à l'ombre attend encore.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1876,7 +1974,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'avais soif. J'ai bu de l'eau. Bravo, Victorina. Tu as fait du bon travail. Le toboggan se repose au soleil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2016,7 +2114,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'avais soif.
+enfant-f|J'ai bu de l'eau.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+narrateur|Le toboggan se repose au soleil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2038,7 +2141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2179,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-04.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Blanche joue au parc avec papa. Le soleil chauffe le toboggan. Blanche court. Sa bouche devient sèche. Elle a soif. Papa est près du banc. Blanche dit : j'ai soif, papa. Papa sourit. Ils rentrent à la maison. Dans la cuisine, papa prend un verre. Il verse de l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt; claire. Blanche prend le verre d'eau. Elle boit une gorgée. C'est frais. Elle boit encore. Papa dit : quand on a soif, on boit de l'eau. Blanche pose le verre. Elle se sent mieux. Elle dit merci. Papa verse encore un peu. Blanche boit une dernière gorgée. L'eau coule douce dans sa gorge.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le toboggan est chaud comme un pain. Le métal brille, tout fort. Une cigale chante dans le platane. Les cheveux de Victorina collent un peu. Le parc sent l'herbe sèche. Victorina habite tout près, avec papa. Maman prépare le goûter, à la maison. Un banc attend à l'ombre. Tu as entendu la cigale, Victorina ? Elle chante, papa. Oui. Elle chante dans le platane. On s'assoit un moment sur le banc ? Oui, papa. Ils s'assoient à l'ombre. Le bois du banc est tiède. En ce moment, Victorina a soif. Sa bouche devient sèche. J'ai soif, papa. On rentre à la maison ? Oui. Ils rentrent. Leurs chaussures font clap, clap. Dans la cuisine, c'est plus frais. Viens. On prend un verre. Papa prend un verre. Il verse de l'eau claire. L'eau chante dans le verre. Tu prends le verre d'eau ? Victorina prend le verre. Elle boit une gorgée. C'est frais. Elle boit encore. Quand on a soif, on boit de l'eau. Dans un verre. Victorina pose le verre. Tu te sens mieux ? Oui, papa. Bravo, Victorina. Tu as bu de l'eau. L'eau coule douce dans sa gorge. Tu restes près de la table ? Oui, papa. On est bien, ici. La cuisine est plus fraîche que le parc. Tu as encore la cigale dans l'oreille ? Un peu. Elle chante loin, maintenant. Victorina tient le verre à deux mains. Une goutte reste sur le bord.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Blanche a &lt;emphasis level="moderate"&gt;soif&lt;/emphasis&gt;. Que prend-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a soif. Que prend-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1575,7 +1575,6 @@
 narrateur|Que prend-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1600,12 +1599,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina avait soif. Elle a pris le verre. Elle a bu de l'eau. Bravo. C'est du bon travail. C'est frais, papa. Oui. L'eau est fraîche. Tu veux encore une gorgée ? Oui. Papa verse encore un peu. Victorina boit une dernière gorgée. Elle pose le verre. Le verre reste sur la table ? Oui, papa.</t>
+          <t>Victorina avait soif. Elle a pris le verre. Elle a bu de l'eau. Bravo. C'est frais, papa. Oui. L'eau est fraîche. Tu veux encore une gorgée ? Oui. Papa verse encore un peu. Victorina boit une dernière gorgée. Elle pose le verre. Le verre reste sur la table ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Blanche avait soif. Elle a pris le verre. Elle a bu de l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. Papa était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina avait soif. Elle a pris le verre. Elle a bu de l'eau. Bravo. C'est frais, papa. Oui. L'eau est fraîche. Tu veux encore une gorgée ? Oui. Papa verse encore un peu. Victorina boit une dernière gorgée. Elle pose le verre. Le verre reste sur la table ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1748,7 +1747,6 @@
 narrateur|Elle a pris le verre.
 narrateur|Elle a bu de l'eau.
 papa|Bravo.
-papa|C'est du bon travail.
 enfant-f|C'est frais, papa.
 papa|Oui. L'eau est fraîche.
 papa|Tu veux encore une gorgée ?
@@ -1760,7 +1758,6 @@
 enfant-f|Oui, papa.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1790,7 +1787,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Blanche retourne au jardin. Le &lt;emphasis level="moderate"&gt;verre&lt;/emphasis&gt; reste sur la table.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On retourne au jardin ? Oui, papa. Victorina prend la main de papa. Le verre reste sur la table. Tu as fini de poser le verre ? Oui. Bravo. Dehors, le platane fait de l'ombre. La cigale chante encore, plus loin. Le toboggan est encore chaud, hein ? Oui. Comme un pain. On reste à l'ombre un moment ? Oui. Merci, papa. Merci, Victorina. Tu as bu de l'eau. Victorina reste près de papa. Le jardin est plus doux, maintenant. Tu as fini de te reposer ? Oui, papa. Bravo. Le banc à l'ombre attend encore.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1949,7 +1946,6 @@
 narrateur|Le banc à l'ombre attend encore.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1974,12 +1970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'avais soif. J'ai bu de l'eau. Bravo, Victorina. Tu as fait du bon travail. Le toboggan se repose au soleil. L'histoire est finie.</t>
+          <t>J'avais soif. J'ai bu de l'eau. Bravo, Victorina. Le toboggan se repose au soleil.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'avais soif. J'ai bu de l'eau. Bravo, Victorina. Le toboggan se repose au soleil.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2117,12 +2113,9 @@
           <t>enfant-f|J'avais soif.
 enfant-f|J'ai bu de l'eau.
 papa|Bravo, Victorina.
-papa|Tu as fait du bon travail.
-narrateur|Le toboggan se repose au soleil.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le toboggan se repose au soleil.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2141,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2186,6 +2179,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-04.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-04.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blanche, papa</t>
+          <t>Victorina, papa</t>
         </is>
       </c>
     </row>
